--- a/data/trans_dic/P74B-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P74B-Clase-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que su pareja percibe algún tipo de pensión</t>
+          <t>Población que su pareja percibe algún tipo de pensión (tasa de respuesta: 96,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,8; 13,1</t>
+          <t>3,84; 12,57</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,71; 15,24</t>
+          <t>4,71; 16,26</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9,25; 21,82</t>
+          <t>9,27; 21,61</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>63,76; 95,94</t>
+          <t>65,09; 95,93</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>34,09; 68,19</t>
+          <t>33,88; 68,94</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>38,41; 69,47</t>
+          <t>38,38; 69,46</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,0; 22,76</t>
+          <t>11,77; 22,48</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>12,38; 24,64</t>
+          <t>12,44; 24,58</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>18,79; 32,39</t>
+          <t>18,29; 32,27</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,99; 11,65</t>
+          <t>2,97; 11,8</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,94; 18,28</t>
+          <t>6,84; 18,05</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,55; 21,22</t>
+          <t>9,31; 20,73</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>43,79; 89,96</t>
+          <t>45,92; 89,63</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>40,65; 71,71</t>
+          <t>39,7; 71,53</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,67; 58,73</t>
+          <t>27,24; 57,92</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,29; 19,96</t>
+          <t>9,2; 20,83</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>15,62; 27,86</t>
+          <t>15,48; 27,79</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>14,56; 26,27</t>
+          <t>14,97; 26,19</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,13; 6,63</t>
+          <t>2,04; 6,83</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9,18; 17,65</t>
+          <t>9,23; 18,03</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,9; 17,01</t>
+          <t>8,79; 17,07</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>63,12; 92,47</t>
+          <t>61,86; 92,32</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>52,31; 76,13</t>
+          <t>51,59; 76,39</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>52,28; 81,55</t>
+          <t>53,54; 80,94</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,57; 14,45</t>
+          <t>7,77; 14,74</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>17,43; 26,5</t>
+          <t>17,23; 26,58</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>16,32; 26,21</t>
+          <t>16,45; 26,12</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,07; 11,48</t>
+          <t>7,16; 11,52</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,97; 14,69</t>
+          <t>9,02; 14,57</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,33; 13,64</t>
+          <t>8,43; 13,86</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>67,28; 83,5</t>
+          <t>66,89; 83,21</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>41,49; 57,7</t>
+          <t>40,96; 57,19</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>45,57; 61,49</t>
+          <t>46,24; 62,1</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,49; 21,86</t>
+          <t>16,23; 21,89</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>17,3; 23,72</t>
+          <t>17,29; 23,86</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>17,68; 24,02</t>
+          <t>17,84; 24,1</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,45; 13,13</t>
+          <t>4,46; 13,09</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>12,45; 23,63</t>
+          <t>12,51; 22,81</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9,89; 18,96</t>
+          <t>9,82; 18,38</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>66,54; 82,83</t>
+          <t>66,52; 83,08</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>54,53; 66,86</t>
+          <t>54,58; 67,04</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>45,18; 58,0</t>
+          <t>45,58; 58,26</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,89; 41,2</t>
+          <t>30,22; 41,41</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>37,04; 47,1</t>
+          <t>37,35; 46,46</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>27,62; 36,26</t>
+          <t>27,92; 36,78</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>43,07; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>84,82; 92,01</t>
+          <t>84,95; 92,25</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>82,39; 89,86</t>
+          <t>82,84; 89,76</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>81,24; 88,81</t>
+          <t>81,38; 88,63</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>85,17; 92,35</t>
+          <t>84,85; 91,99</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>82,41; 89,91</t>
+          <t>82,27; 89,37</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>79,52; 87,51</t>
+          <t>79,74; 87,47</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,15; 8,94</t>
+          <t>6,23; 9,15</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>10,81; 14,6</t>
+          <t>10,81; 14,51</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10,8; 14,43</t>
+          <t>10,81; 14,34</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>79,79; 85,74</t>
+          <t>79,66; 85,73</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>64,8; 71,32</t>
+          <t>64,63; 71,09</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>62,41; 68,97</t>
+          <t>62,5; 68,85</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>28,32; 32,15</t>
+          <t>28,15; 32,49</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>32,72; 36,81</t>
+          <t>32,73; 36,79</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>31,68; 35,92</t>
+          <t>31,72; 35,86</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que su pareja percibe algún tipo de pensión</t>
+          <t>Población que su pareja percibe algún tipo de pensión (tasa de respuesta: 96,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>6677; 22994</t>
+          <t>6742; 22069</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7382; 23875</t>
+          <t>7383; 25474</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12037; 28406</t>
+          <t>12065; 28127</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15726; 23664</t>
+          <t>16054; 23662</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>14449; 28903</t>
+          <t>14360; 29219</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16523; 29886</t>
+          <t>16510; 29879</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>24036; 45578</t>
+          <t>23566; 45010</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>24649; 49045</t>
+          <t>24761; 48927</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>32547; 56095</t>
+          <t>31679; 55894</t>
         </is>
       </c>
     </row>
@@ -1802,47 +1802,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4584; 17881</t>
+          <t>4563; 18112</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11641; 30640</t>
+          <t>11471; 30267</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15015; 33359</t>
+          <t>14625; 32579</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8855; 18192</t>
+          <t>9286; 18126</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>18545; 32712</t>
+          <t>18108; 32629</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10350; 24634</t>
+          <t>11426; 24296</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16139; 34673</t>
+          <t>15985; 36190</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>33307; 59422</t>
+          <t>33019; 59269</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>28996; 52315</t>
+          <t>29805; 52142</t>
         </is>
       </c>
     </row>
@@ -1965,47 +1965,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>6145; 19137</t>
+          <t>5886; 19710</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>29195; 56154</t>
+          <t>29369; 57358</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>23823; 45539</t>
+          <t>23536; 45685</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>17731; 25976</t>
+          <t>17377; 25935</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>34090; 49609</t>
+          <t>33617; 49782</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>24378; 38030</t>
+          <t>24967; 37746</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23975; 45740</t>
+          <t>24600; 46643</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>66811; 101592</t>
+          <t>66066; 101896</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>51280; 82381</t>
+          <t>51715; 82084</t>
         </is>
       </c>
     </row>
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>45053; 73116</t>
+          <t>45600; 73413</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>47397; 77623</t>
+          <t>47678; 76980</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>44551; 72988</t>
+          <t>45097; 74140</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>74900; 92960</t>
+          <t>74473; 92632</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>66432; 92384</t>
+          <t>65589; 91568</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>73860; 99662</t>
+          <t>74950; 100655</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>123440; 163603</t>
+          <t>121441; 163854</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>119113; 163331</t>
+          <t>119064; 164292</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>123275; 167430</t>
+          <t>124379; 168011</t>
         </is>
       </c>
     </row>
@@ -2291,47 +2291,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>6959; 20532</t>
+          <t>6978; 20472</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>25287; 48003</t>
+          <t>25403; 46326</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>25769; 49390</t>
+          <t>25578; 47865</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>72036; 89673</t>
+          <t>72009; 89944</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>143799; 176329</t>
+          <t>143947; 176794</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>108151; 138850</t>
+          <t>109122; 139478</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>79084; 109019</t>
+          <t>79971; 109581</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>172929; 219871</t>
+          <t>174370; 216884</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>138074; 181243</t>
+          <t>139566; 183855</t>
         </is>
       </c>
     </row>
@@ -2454,47 +2454,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>782; 1815</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 964</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 1635</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>270996; 293980</t>
+          <t>271427; 294747</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>278075; 303287</t>
+          <t>279606; 302933</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>290793; 317894</t>
+          <t>291284; 317244</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>273656; 296731</t>
+          <t>272630; 295568</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>279165; 304578</t>
+          <t>278691; 302755</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>289545; 318640</t>
+          <t>290333; 318492</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>86909; 126286</t>
+          <t>87961; 129242</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>148641; 200744</t>
+          <t>148660; 199512</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>146527; 195771</t>
+          <t>146637; 194536</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>488369; 524803</t>
+          <t>487602; 524709</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>592607; 652211</t>
+          <t>591036; 650157</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>556055; 614557</t>
+          <t>556855; 613437</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>573382; 650946</t>
+          <t>569996; 657843</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>749234; 842971</t>
+          <t>749580; 842464</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>711984; 807434</t>
+          <t>712868; 805915</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P74B-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P74B-Clase-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,84; 12,57</t>
+          <t>4,05; 12,9</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,71; 16,26</t>
+          <t>4,48; 15,04</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9,27; 21,61</t>
+          <t>9,63; 22,11</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>65,09; 95,93</t>
+          <t>66,3; 96,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>33,88; 68,94</t>
+          <t>34,88; 67,52</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>38,38; 69,46</t>
+          <t>39,28; 68,93</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,77; 22,48</t>
+          <t>11,93; 23,39</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>12,44; 24,58</t>
+          <t>12,41; 25,43</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>18,29; 32,27</t>
+          <t>18,53; 31,75</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,97; 11,8</t>
+          <t>2,74; 11,35</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,84; 18,05</t>
+          <t>7,28; 18,75</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,31; 20,73</t>
+          <t>9,18; 20,98</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>45,92; 89,63</t>
+          <t>42,34; 89,57</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>39,7; 71,53</t>
+          <t>40,28; 71,09</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,24; 57,92</t>
+          <t>26,28; 59,86</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,2; 20,83</t>
+          <t>9,02; 19,93</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>15,48; 27,79</t>
+          <t>15,43; 28,58</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>14,97; 26,19</t>
+          <t>14,77; 26,39</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,04; 6,83</t>
+          <t>2,13; 6,61</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9,23; 18,03</t>
+          <t>9,39; 18,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,79; 17,07</t>
+          <t>8,84; 17,15</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>61,86; 92,32</t>
+          <t>60,92; 91,21</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>51,59; 76,39</t>
+          <t>51,73; 75,92</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>53,54; 80,94</t>
+          <t>52,81; 81,32</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,77; 14,74</t>
+          <t>7,61; 14,33</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>17,23; 26,58</t>
+          <t>17,54; 26,64</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>16,45; 26,12</t>
+          <t>16,35; 26,15</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,16; 11,52</t>
+          <t>7,12; 11,56</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,02; 14,57</t>
+          <t>9,09; 15,11</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,43; 13,86</t>
+          <t>7,93; 13,46</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>66,89; 83,21</t>
+          <t>66,86; 83,37</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>40,96; 57,19</t>
+          <t>40,52; 57,44</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>46,24; 62,1</t>
+          <t>45,88; 62,42</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,23; 21,89</t>
+          <t>16,46; 22,11</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>17,29; 23,86</t>
+          <t>17,64; 23,88</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>17,84; 24,1</t>
+          <t>18,01; 23,86</t>
         </is>
       </c>
     </row>
@@ -1118,54 +1118,54 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,46; 13,09</t>
+          <t>4,52; 13,79</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>12,51; 22,81</t>
+          <t>12,24; 23,17</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9,82; 18,38</t>
+          <t>9,92; 18,36</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>66,52; 83,08</t>
+          <t>65,88; 82,41</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>54,58; 67,04</t>
+          <t>54,82; 66,87</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>45,58; 58,26</t>
+          <t>44,43; 57,45</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,22; 41,41</t>
+          <t>30,12; 41,43</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>37,35; 46,46</t>
+          <t>37,79; 47,33</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>27,92; 36,78</t>
+          <t>28,01; 36,27</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1243,32 +1243,32 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>84,95; 92,25</t>
+          <t>85,1; 92,05</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>82,84; 89,76</t>
+          <t>82,21; 89,86</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>81,38; 88,63</t>
+          <t>81,05; 89,14</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>84,85; 91,99</t>
+          <t>85,0; 92,37</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>82,27; 89,37</t>
+          <t>82,09; 89,6</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>79,74; 87,47</t>
+          <t>79,07; 87,54</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,23; 9,15</t>
+          <t>6,14; 8,86</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>10,81; 14,51</t>
+          <t>10,75; 14,57</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10,81; 14,34</t>
+          <t>10,77; 14,34</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>79,66; 85,73</t>
+          <t>79,55; 85,86</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>64,63; 71,09</t>
+          <t>64,43; 71,11</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>62,5; 68,85</t>
+          <t>62,3; 69,33</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>28,15; 32,49</t>
+          <t>28,29; 32,54</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>32,73; 36,79</t>
+          <t>32,55; 36,77</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>31,72; 35,86</t>
+          <t>31,87; 36,04</t>
         </is>
       </c>
     </row>
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>6742; 22069</t>
+          <t>7117; 22657</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7383; 25474</t>
+          <t>7016; 23558</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12065; 28127</t>
+          <t>12541; 28788</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>16054; 23662</t>
+          <t>16355; 23679</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>14360; 29219</t>
+          <t>14782; 28618</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16510; 29879</t>
+          <t>16899; 29653</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>23566; 45010</t>
+          <t>23888; 46831</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>24761; 48927</t>
+          <t>24696; 50627</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>31679; 55894</t>
+          <t>32086; 54995</t>
         </is>
       </c>
     </row>
@@ -1802,47 +1802,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4563; 18112</t>
+          <t>4207; 17429</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11471; 30267</t>
+          <t>12204; 31429</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14625; 32579</t>
+          <t>14421; 32978</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9286; 18126</t>
+          <t>8562; 18113</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>18108; 32629</t>
+          <t>18373; 32427</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11426; 24296</t>
+          <t>11023; 25109</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15985; 36190</t>
+          <t>15669; 34633</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>33019; 59269</t>
+          <t>32896; 60960</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>29805; 52142</t>
+          <t>29407; 52551</t>
         </is>
       </c>
     </row>
@@ -1965,47 +1965,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>5886; 19710</t>
+          <t>6141; 19070</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>29369; 57358</t>
+          <t>29865; 57757</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>23536; 45685</t>
+          <t>23670; 45904</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>17377; 25935</t>
+          <t>17113; 25622</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>33617; 49782</t>
+          <t>33713; 49474</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>24967; 37746</t>
+          <t>24628; 37920</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>24600; 46643</t>
+          <t>24087; 45358</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>66066; 101896</t>
+          <t>67252; 102132</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>51715; 82084</t>
+          <t>51374; 82180</t>
         </is>
       </c>
     </row>
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>45600; 73413</t>
+          <t>45346; 73669</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>47678; 76980</t>
+          <t>48034; 79846</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>45097; 74140</t>
+          <t>42436; 72026</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>74473; 92632</t>
+          <t>74435; 92816</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>65589; 91568</t>
+          <t>64873; 91967</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>74950; 100655</t>
+          <t>74361; 101166</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>121441; 163854</t>
+          <t>123172; 165501</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>119064; 164292</t>
+          <t>121433; 164447</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>124379; 168011</t>
+          <t>125569; 166318</t>
         </is>
       </c>
     </row>
@@ -2291,54 +2291,54 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>6978; 20472</t>
+          <t>7064; 21568</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>25403; 46326</t>
+          <t>24872; 47056</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>25578; 47865</t>
+          <t>25826; 47826</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>72009; 89944</t>
+          <t>71318; 89211</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>143947; 176794</t>
+          <t>144571; 176354</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>109122; 139478</t>
+          <t>106363; 137532</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>79971; 109581</t>
+          <t>79695; 109637</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>174370; 216884</t>
+          <t>176407; 220967</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>139566; 183855</t>
+          <t>140009; 181267</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2469,32 +2469,32 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>271427; 294747</t>
+          <t>271910; 294109</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>279606; 302933</t>
+          <t>277465; 303289</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>291284; 317244</t>
+          <t>290102; 319066</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>272630; 295568</t>
+          <t>273120; 296817</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>278691; 302755</t>
+          <t>278071; 303526</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>290333; 318492</t>
+          <t>287922; 318734</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>87961; 129242</t>
+          <t>86750; 125132</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>148660; 199512</t>
+          <t>147863; 200353</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>146637; 194536</t>
+          <t>146115; 194579</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>487602; 524709</t>
+          <t>486902; 525540</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>591036; 650157</t>
+          <t>589258; 650270</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>556855; 613437</t>
+          <t>555097; 617764</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>569996; 657843</t>
+          <t>572778; 658955</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>749580; 842464</t>
+          <t>745411; 842028</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>712868; 805915</t>
+          <t>716450; 810070</t>
         </is>
       </c>
     </row>
